--- a/crawl_test.xlsx
+++ b/crawl_test.xlsx
@@ -5290,12 +5290,12 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>tbody</t>
+          <t>table.table_list</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>td:nth-child(3)</t>
+          <t>td:nth-child(2)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11722,7 +11722,11 @@
           <t>td:nth-child(5)</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>{"sleep": 15}</t>
+        </is>
+      </c>
       <c r="K224" t="inlineStr">
         <is>
           <t>active</t>
